--- a/StructureDefinition-openimis-claim-administrator-practitioner.xlsx
+++ b/StructureDefinition-openimis-claim-administrator-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-26T15:39:34+00:00</t>
+    <t>2025-09-08T11:14:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -10464,7 +10464,7 @@
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>22</v>
@@ -14565,7 +14565,7 @@
         <v>80</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>22</v>
@@ -14916,7 +14916,7 @@
         <v>80</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>22</v>
@@ -15035,7 +15035,7 @@
         <v>80</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>22</v>
@@ -16084,7 +16084,7 @@
         <v>80</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>22</v>

--- a/StructureDefinition-openimis-claim-administrator-practitioner.xlsx
+++ b/StructureDefinition-openimis-claim-administrator-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:14:40+00:00</t>
+    <t>2025-09-08T11:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-openimis-claim-administrator-practitioner.xlsx
+++ b/StructureDefinition-openimis-claim-administrator-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:37:47+00:00</t>
+    <t>2025-09-08T11:49:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
